--- a/AAII_Financials/Yearly/HENOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HENOY_YR_FIN.xlsx
@@ -731,10 +731,10 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>11828100</v>
+        <v>11769400</v>
       </c>
       <c r="E9" s="3">
-        <v>11145000</v>
+        <v>11040500</v>
       </c>
       <c r="F9" s="3">
         <v>12901500</v>
@@ -758,10 +758,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12235500</v>
+        <v>12294200</v>
       </c>
       <c r="E10" s="3">
-        <v>11203000</v>
+        <v>11307600</v>
       </c>
       <c r="F10" s="3">
         <v>10878700</v>
@@ -798,10 +798,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>739700</v>
+        <v>720900</v>
       </c>
       <c r="E12" s="3">
-        <v>656400</v>
+        <v>654300</v>
       </c>
       <c r="F12" s="3">
         <v>642200</v>
@@ -852,10 +852,10 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-54000</v>
+        <v>77500</v>
       </c>
       <c r="E14" s="3">
-        <v>5200</v>
+        <v>213300</v>
       </c>
       <c r="F14" s="3">
         <v>517300</v>
@@ -916,10 +916,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>20821900</v>
+        <v>20690400</v>
       </c>
       <c r="E17" s="3">
-        <v>19423300</v>
+        <v>19215200</v>
       </c>
       <c r="F17" s="3">
         <v>21046800</v>
@@ -943,10 +943,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3241800</v>
+        <v>3373300</v>
       </c>
       <c r="E18" s="3">
-        <v>2924700</v>
+        <v>3132800</v>
       </c>
       <c r="F18" s="3">
         <v>2733500</v>
@@ -1010,10 +1010,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3710200</v>
+        <v>3841700</v>
       </c>
       <c r="E21" s="3">
-        <v>3356500</v>
+        <v>3564600</v>
       </c>
       <c r="F21" s="3">
         <v>3193300</v>
